--- a/src/main/resources/espacios/Daily/0 -  Job.xlsx
+++ b/src/main/resources/espacios/Daily/0 -  Job.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Daily" sheetId="1" state="visible" r:id="rId3"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2810" uniqueCount="2124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2812" uniqueCount="2124">
   <si>
     <t xml:space="preserve">Hi, I'm Juan and I'm working on implementing the search function.</t>
   </si>
@@ -6485,7 +6485,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -6503,10 +6503,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6638,7 +6634,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F60"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="88.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="84.54"/>
@@ -6955,6 +6951,9 @@
       <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="F21" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -7251,6 +7250,9 @@
       <c r="C41" s="2"/>
       <c r="D41" s="1" t="s">
         <v>123</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7555,7 +7557,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F84"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="91.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="113.44"/>
@@ -8749,7 +8751,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F84"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="122.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="149.77"/>
@@ -9498,7 +9500,7 @@
       <c r="A54" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="1" t="s">
         <v>593</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -9512,7 +9514,7 @@
       <c r="A55" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="1" t="s">
         <v>596</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -9526,7 +9528,7 @@
       <c r="A56" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="1" t="s">
         <v>599</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -9540,7 +9542,7 @@
       <c r="A57" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="1" t="s">
         <v>602</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -9554,7 +9556,7 @@
       <c r="A58" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="1" t="s">
         <v>605</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -9568,7 +9570,7 @@
       <c r="A59" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="1" t="s">
         <v>608</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -9582,7 +9584,7 @@
       <c r="A60" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="1" t="s">
         <v>611</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -9596,7 +9598,7 @@
       <c r="A61" s="4" t="s">
         <v>613</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="1" t="s">
         <v>614</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -9610,7 +9612,7 @@
       <c r="A62" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="1" t="s">
         <v>617</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -9624,7 +9626,7 @@
       <c r="A63" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="1" t="s">
         <v>620</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -9943,7 +9945,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="118.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="153.27"/>
@@ -10245,7 +10247,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>748</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -10257,7 +10259,7 @@
       <c r="F22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>751</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -10271,7 +10273,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>754</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -10285,7 +10287,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>757</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -10299,7 +10301,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>760</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -10313,7 +10315,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>763</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -10327,7 +10329,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>766</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -10341,7 +10343,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>769</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -10355,7 +10357,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>772</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -10369,7 +10371,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>775</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -10383,7 +10385,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>778</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -10397,7 +10399,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>781</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -10411,7 +10413,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>784</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -10425,7 +10427,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>787</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -10439,7 +10441,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>790</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -10453,7 +10455,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>793</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -10467,7 +10469,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>796</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -10481,7 +10483,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>799</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -10495,7 +10497,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>802</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -10509,7 +10511,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>805</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -10523,7 +10525,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>808</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -10537,7 +10539,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>811</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -10549,7 +10551,7 @@
       <c r="F43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>814</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -10563,7 +10565,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>817</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -10577,7 +10579,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>820</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -10591,7 +10593,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>823</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -10605,7 +10607,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>826</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -10619,7 +10621,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>829</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -10633,7 +10635,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>832</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -10647,7 +10649,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>835</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -10661,7 +10663,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>838</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -10675,7 +10677,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>841</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -10689,7 +10691,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>844</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -10703,7 +10705,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>847</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -10717,7 +10719,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>850</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -10731,7 +10733,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>853</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -10745,7 +10747,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>856</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -10759,7 +10761,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>859</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -10773,7 +10775,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>862</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -10787,7 +10789,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>865</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -10801,7 +10803,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>868</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -10815,7 +10817,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>871</v>
       </c>
       <c r="B63" s="3" t="s">
@@ -10829,7 +10831,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>874</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -10841,7 +10843,7 @@
       <c r="F64" s="1"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>877</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -10855,7 +10857,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>880</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -10869,7 +10871,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>883</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -10883,7 +10885,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>886</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -10897,7 +10899,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>889</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -10911,7 +10913,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>892</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -10925,7 +10927,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>895</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -10939,7 +10941,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>898</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -10953,7 +10955,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>901</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -10967,7 +10969,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>904</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -10981,7 +10983,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>907</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -10995,7 +10997,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>910</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -11009,7 +11011,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>913</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -11023,7 +11025,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>916</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -11037,7 +11039,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>919</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -11051,7 +11053,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>922</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -11065,7 +11067,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="5" t="s">
         <v>925</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -11079,7 +11081,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
         <v>928</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -11093,7 +11095,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>931</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -11107,7 +11109,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>934</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -11121,7 +11123,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>937</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -11133,7 +11135,7 @@
       <c r="F85" s="1"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>940</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -11147,7 +11149,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>943</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -11161,7 +11163,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>946</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -11175,7 +11177,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="5" t="s">
         <v>949</v>
       </c>
       <c r="B89" s="3" t="s">
@@ -11189,7 +11191,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="5" t="s">
         <v>952</v>
       </c>
       <c r="B90" s="3" t="s">
@@ -11203,7 +11205,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>955</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -11217,7 +11219,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="5" t="s">
         <v>958</v>
       </c>
       <c r="B92" s="3" t="s">
@@ -11231,7 +11233,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>961</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -11245,7 +11247,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="5" t="s">
         <v>964</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -11259,7 +11261,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>967</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -11273,7 +11275,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="5" t="s">
         <v>970</v>
       </c>
       <c r="B96" s="3" t="s">
@@ -11287,7 +11289,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="5" t="s">
         <v>973</v>
       </c>
       <c r="B97" s="3" t="s">
@@ -11301,7 +11303,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>976</v>
       </c>
       <c r="B98" s="3" t="s">
@@ -11315,7 +11317,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="5" t="s">
         <v>979</v>
       </c>
       <c r="B99" s="3" t="s">
@@ -11329,7 +11331,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="5" t="s">
         <v>982</v>
       </c>
       <c r="B100" s="3" t="s">
@@ -11343,7 +11345,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="5" t="s">
         <v>985</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -11357,7 +11359,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="5" t="s">
         <v>988</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -11371,7 +11373,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="5" t="s">
         <v>991</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -11385,7 +11387,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="5" t="s">
         <v>994</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -11399,7 +11401,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="5" t="s">
         <v>997</v>
       </c>
       <c r="B105" s="3" t="s">
@@ -11429,7 +11431,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="124.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="165.67"/>
@@ -12910,7 +12912,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F131"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="113.44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="138.2"/>
@@ -13211,10 +13213,10 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>1377</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="1" t="s">
         <v>1378</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -13222,10 +13224,10 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>1380</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="1" t="s">
         <v>1381</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -13236,10 +13238,10 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>1383</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="1" t="s">
         <v>1384</v>
       </c>
       <c r="D24" s="3" t="s">
@@ -13250,10 +13252,10 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>1386</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="1" t="s">
         <v>1387</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -13264,10 +13266,10 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>1389</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="1" t="s">
         <v>1390</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -13278,10 +13280,10 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>1392</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="1" t="s">
         <v>1393</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -13292,10 +13294,10 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>1395</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="1" t="s">
         <v>1396</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -13306,10 +13308,10 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>1398</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="1" t="s">
         <v>1399</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -13320,10 +13322,10 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>1401</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="1" t="s">
         <v>1402</v>
       </c>
       <c r="D30" s="3" t="s">
@@ -13334,10 +13336,10 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>1404</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="1" t="s">
         <v>1405</v>
       </c>
       <c r="D31" s="3" t="s">
@@ -13348,10 +13350,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>1407</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="1" t="s">
         <v>1408</v>
       </c>
       <c r="D32" s="3" t="s">
@@ -13362,10 +13364,10 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>1410</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="1" t="s">
         <v>1411</v>
       </c>
       <c r="D33" s="3" t="s">
@@ -13376,10 +13378,10 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>1413</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="1" t="s">
         <v>1414</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -13390,10 +13392,10 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>1416</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>1417</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -13404,10 +13406,10 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>1419</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="1" t="s">
         <v>1420</v>
       </c>
       <c r="D36" s="3" t="s">
@@ -13418,10 +13420,10 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>1422</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="1" t="s">
         <v>1423</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -13432,10 +13434,10 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>1425</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="1" t="s">
         <v>1426</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -13446,10 +13448,10 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>1428</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="1" t="s">
         <v>1429</v>
       </c>
       <c r="D39" s="3" t="s">
@@ -13460,10 +13462,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>1431</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="1" t="s">
         <v>1432</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -13474,10 +13476,10 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>1434</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="1" t="s">
         <v>1435</v>
       </c>
       <c r="D41" s="3" t="s">
@@ -13488,10 +13490,10 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>1437</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="1" t="s">
         <v>1438</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -13502,7 +13504,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>1440</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -13513,10 +13515,10 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>1263</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="1" t="s">
         <v>1443</v>
       </c>
       <c r="D44" s="3" t="s">
@@ -13527,10 +13529,10 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>1257</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="1" t="s">
         <v>1444</v>
       </c>
       <c r="D45" s="3" t="s">
@@ -13541,10 +13543,10 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>1445</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="1" t="s">
         <v>1446</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -13555,10 +13557,10 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>1284</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="1" t="s">
         <v>1285</v>
       </c>
       <c r="D47" s="3" t="s">
@@ -13569,10 +13571,10 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>1448</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="1" t="s">
         <v>1449</v>
       </c>
       <c r="D48" s="3" t="s">
@@ -13583,10 +13585,10 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>1451</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="1" t="s">
         <v>1452</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -13597,10 +13599,10 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>1454</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="1" t="s">
         <v>1455</v>
       </c>
       <c r="D50" s="3" t="s">
@@ -13611,10 +13613,10 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>1457</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="1" t="s">
         <v>1458</v>
       </c>
       <c r="D51" s="3" t="s">
@@ -13625,10 +13627,10 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>1460</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="1" t="s">
         <v>1461</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -13639,10 +13641,10 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>1463</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="1" t="s">
         <v>1464</v>
       </c>
       <c r="D53" s="3" t="s">
@@ -13653,10 +13655,10 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>1466</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="1" t="s">
         <v>1467</v>
       </c>
       <c r="D54" s="3" t="s">
@@ -13667,10 +13669,10 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>1469</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="1" t="s">
         <v>1470</v>
       </c>
       <c r="D55" s="3" t="s">
@@ -13681,10 +13683,10 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="1" t="s">
         <v>1473</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -13695,10 +13697,10 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>1475</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="1" t="s">
         <v>1476</v>
       </c>
       <c r="D57" s="3" t="s">
@@ -13709,10 +13711,10 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>1478</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="1" t="s">
         <v>1479</v>
       </c>
       <c r="D58" s="3" t="s">
@@ -13723,10 +13725,10 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>1481</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="1" t="s">
         <v>1482</v>
       </c>
       <c r="D59" s="3" t="s">
@@ -13737,10 +13739,10 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>1484</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="1" t="s">
         <v>1485</v>
       </c>
       <c r="D60" s="3" t="s">
@@ -13751,10 +13753,10 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>1487</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="1" t="s">
         <v>1488</v>
       </c>
       <c r="D61" s="3" t="s">
@@ -13765,10 +13767,10 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>1490</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="1" t="s">
         <v>1491</v>
       </c>
       <c r="D62" s="3" t="s">
@@ -13779,10 +13781,10 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>1493</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="1" t="s">
         <v>1494</v>
       </c>
       <c r="D63" s="3" t="s">
@@ -13793,7 +13795,7 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>1496</v>
       </c>
       <c r="B64" s="3" t="s">
@@ -13804,7 +13806,7 @@
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>1499</v>
       </c>
       <c r="B65" s="3" t="s">
@@ -13818,7 +13820,7 @@
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>1502</v>
       </c>
       <c r="B66" s="3" t="s">
@@ -13832,7 +13834,7 @@
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>1505</v>
       </c>
       <c r="B67" s="3" t="s">
@@ -13846,7 +13848,7 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>1508</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -13860,7 +13862,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>1511</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -13874,7 +13876,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>1514</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -13888,7 +13890,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>1517</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -13902,7 +13904,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="5" t="s">
         <v>1520</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -13916,7 +13918,7 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="6" t="s">
+      <c r="A73" s="5" t="s">
         <v>1523</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -13930,7 +13932,7 @@
       </c>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="s">
+      <c r="A74" s="5" t="s">
         <v>1526</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -13944,7 +13946,7 @@
       </c>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="s">
+      <c r="A75" s="5" t="s">
         <v>1529</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -13958,7 +13960,7 @@
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="s">
+      <c r="A76" s="5" t="s">
         <v>1532</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -13972,7 +13974,7 @@
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
+      <c r="A77" s="5" t="s">
         <v>1535</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -13986,7 +13988,7 @@
       </c>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="6" t="s">
+      <c r="A78" s="5" t="s">
         <v>1538</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -14000,7 +14002,7 @@
       </c>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6" t="s">
+      <c r="A79" s="5" t="s">
         <v>1541</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -14014,7 +14016,7 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="6" t="s">
+      <c r="A80" s="5" t="s">
         <v>1544</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -14028,7 +14030,7 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="6" t="s">
+      <c r="A81" s="5" t="s">
         <v>1547</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -14042,7 +14044,7 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="6" t="s">
+      <c r="A82" s="5" t="s">
         <v>1550</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -14056,7 +14058,7 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="6" t="s">
+      <c r="A83" s="5" t="s">
         <v>1553</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -14070,7 +14072,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="6" t="s">
+      <c r="A84" s="5" t="s">
         <v>1556</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -14084,7 +14086,7 @@
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="6" t="s">
+      <c r="A85" s="5" t="s">
         <v>1559</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -14095,7 +14097,7 @@
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="6" t="s">
+      <c r="A86" s="5" t="s">
         <v>1562</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -14109,7 +14111,7 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="5" t="s">
         <v>1565</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -14123,7 +14125,7 @@
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="6" t="s">
+      <c r="A88" s="5" t="s">
         <v>1568</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -14137,7 +14139,7 @@
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="6" t="s">
+      <c r="A89" s="5" t="s">
         <v>1571</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -14151,7 +14153,7 @@
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6" t="s">
+      <c r="A90" s="5" t="s">
         <v>1574</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -14165,7 +14167,7 @@
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6" t="s">
+      <c r="A91" s="5" t="s">
         <v>1577</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -14179,7 +14181,7 @@
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6" t="s">
+      <c r="A92" s="5" t="s">
         <v>1580</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -14193,7 +14195,7 @@
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6" t="s">
+      <c r="A93" s="5" t="s">
         <v>1583</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -14207,7 +14209,7 @@
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6" t="s">
+      <c r="A94" s="5" t="s">
         <v>1586</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -14221,7 +14223,7 @@
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6" t="s">
+      <c r="A95" s="5" t="s">
         <v>1589</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -14235,7 +14237,7 @@
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6" t="s">
+      <c r="A96" s="5" t="s">
         <v>1592</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -14249,7 +14251,7 @@
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6" t="s">
+      <c r="A97" s="5" t="s">
         <v>1595</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -14263,7 +14265,7 @@
       </c>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="5" t="s">
         <v>1598</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -14277,7 +14279,7 @@
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6" t="s">
+      <c r="A99" s="5" t="s">
         <v>1601</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -14291,7 +14293,7 @@
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="s">
+      <c r="A100" s="5" t="s">
         <v>1604</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -14305,7 +14307,7 @@
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6" t="s">
+      <c r="A101" s="5" t="s">
         <v>1607</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -14319,7 +14321,7 @@
       </c>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6" t="s">
+      <c r="A102" s="5" t="s">
         <v>1610</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -14333,7 +14335,7 @@
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6" t="s">
+      <c r="A103" s="5" t="s">
         <v>1613</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -14347,7 +14349,7 @@
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6" t="s">
+      <c r="A104" s="5" t="s">
         <v>1616</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -14361,7 +14363,7 @@
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6" t="s">
+      <c r="A105" s="5" t="s">
         <v>1619</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -14375,7 +14377,7 @@
       </c>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6" t="s">
+      <c r="A106" s="5" t="s">
         <v>1622</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -14386,7 +14388,7 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6" t="s">
+      <c r="A107" s="5" t="s">
         <v>1624</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -14400,7 +14402,7 @@
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6" t="s">
+      <c r="A108" s="5" t="s">
         <v>1627</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -14414,7 +14416,7 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6" t="s">
+      <c r="A109" s="5" t="s">
         <v>1630</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -14428,7 +14430,7 @@
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6" t="s">
+      <c r="A110" s="5" t="s">
         <v>1633</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -14442,7 +14444,7 @@
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6" t="s">
+      <c r="A111" s="5" t="s">
         <v>1636</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -14456,7 +14458,7 @@
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6" t="s">
+      <c r="A112" s="5" t="s">
         <v>1639</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -14470,7 +14472,7 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6" t="s">
+      <c r="A113" s="5" t="s">
         <v>1642</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -14484,7 +14486,7 @@
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="6" t="s">
+      <c r="A114" s="5" t="s">
         <v>1645</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -14498,7 +14500,7 @@
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6" t="s">
+      <c r="A115" s="5" t="s">
         <v>1648</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -14512,7 +14514,7 @@
       </c>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="6" t="s">
+      <c r="A116" s="5" t="s">
         <v>1651</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -14526,7 +14528,7 @@
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6" t="s">
+      <c r="A117" s="5" t="s">
         <v>1654</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -14540,7 +14542,7 @@
       </c>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6" t="s">
+      <c r="A118" s="5" t="s">
         <v>1657</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -14554,7 +14556,7 @@
       </c>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="5" t="s">
         <v>1660</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -14568,7 +14570,7 @@
       </c>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="6" t="s">
+      <c r="A120" s="5" t="s">
         <v>1663</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -14582,7 +14584,7 @@
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="6" t="s">
+      <c r="A121" s="5" t="s">
         <v>1666</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -14596,7 +14598,7 @@
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="6" t="s">
+      <c r="A122" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -14610,7 +14612,7 @@
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="6" t="s">
+      <c r="A123" s="5" t="s">
         <v>1672</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -14624,7 +14626,7 @@
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="6" t="s">
+      <c r="A124" s="5" t="s">
         <v>1675</v>
       </c>
       <c r="B124" s="2" t="s">
@@ -14638,7 +14640,7 @@
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6" t="s">
+      <c r="A125" s="5" t="s">
         <v>1678</v>
       </c>
       <c r="B125" s="2" t="s">
@@ -14652,7 +14654,7 @@
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="6" t="s">
+      <c r="A126" s="5" t="s">
         <v>1681</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -14667,23 +14669,23 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2"/>
-      <c r="B127" s="5"/>
+      <c r="B127" s="1"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2"/>
-      <c r="B128" s="5"/>
+      <c r="B128" s="1"/>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="2"/>
-      <c r="B129" s="5"/>
+      <c r="B129" s="1"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2"/>
-      <c r="B130" s="5"/>
+      <c r="B130" s="1"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
-      <c r="B131" s="5"/>
+      <c r="B131" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -14702,7 +14704,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F84"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="95.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="121.14"/>
@@ -15892,7 +15894,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F63"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="96.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="113.01"/>
@@ -15902,7 +15904,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>1935</v>
       </c>
       <c r="B1" s="3" t="s">
@@ -15913,7 +15915,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1938</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -15927,7 +15929,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>1941</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -15941,7 +15943,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>1944</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -15955,7 +15957,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>1947</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -15969,7 +15971,7 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>1950</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -15983,7 +15985,7 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>1953</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -15997,7 +15999,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>1956</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -16011,7 +16013,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>1959</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -16025,7 +16027,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>1962</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -16039,7 +16041,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>1965</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -16053,7 +16055,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>1968</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -16067,7 +16069,7 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>1971</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -16081,7 +16083,7 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>1974</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -16095,7 +16097,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>1977</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -16109,7 +16111,7 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>1980</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -16123,7 +16125,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>1983</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -16137,7 +16139,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>1986</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -16151,7 +16153,7 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="5" t="s">
         <v>1989</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -16165,7 +16167,7 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="5" t="s">
         <v>1992</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -16179,7 +16181,7 @@
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="5" t="s">
         <v>1995</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -16193,7 +16195,7 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="5" t="s">
         <v>1998</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -16204,7 +16206,7 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="5" t="s">
         <v>2001</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -16218,7 +16220,7 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>2004</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -16232,7 +16234,7 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>2007</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -16246,7 +16248,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="5" t="s">
         <v>2010</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -16260,7 +16262,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="5" t="s">
         <v>2013</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -16274,7 +16276,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="5" t="s">
         <v>2016</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -16288,7 +16290,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="5" t="s">
         <v>2019</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -16302,7 +16304,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="5" t="s">
         <v>2022</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -16316,7 +16318,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="5" t="s">
         <v>2025</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -16330,7 +16332,7 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>2028</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -16344,7 +16346,7 @@
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="5" t="s">
         <v>2031</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -16358,7 +16360,7 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="5" t="s">
         <v>2034</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -16372,7 +16374,7 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="5" t="s">
         <v>2037</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -16386,7 +16388,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="5" t="s">
         <v>2040</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -16400,7 +16402,7 @@
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="5" t="s">
         <v>2043</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -16414,7 +16416,7 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="5" t="s">
         <v>2046</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -16428,7 +16430,7 @@
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="5" t="s">
         <v>2049</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -16442,7 +16444,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="5" t="s">
         <v>2052</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -16456,7 +16458,7 @@
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="5" t="s">
         <v>2055</v>
       </c>
       <c r="B41" s="3" t="s">
@@ -16470,7 +16472,7 @@
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>2058</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -16484,7 +16486,7 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>2061</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -16495,7 +16497,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>2064</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -16509,7 +16511,7 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="5" t="s">
         <v>2067</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -16523,7 +16525,7 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>2070</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -16537,7 +16539,7 @@
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>2073</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -16551,7 +16553,7 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>2076</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -16565,7 +16567,7 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="5" t="s">
         <v>2079</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -16579,7 +16581,7 @@
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="5" t="s">
         <v>2082</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -16593,7 +16595,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="5" t="s">
         <v>2085</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -16607,7 +16609,7 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
         <v>2088</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -16621,7 +16623,7 @@
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="5" t="s">
         <v>2091</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -16635,7 +16637,7 @@
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="5" t="s">
         <v>2094</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -16649,7 +16651,7 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="5" t="s">
         <v>2097</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -16663,7 +16665,7 @@
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="5" t="s">
         <v>2100</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -16677,7 +16679,7 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="5" t="s">
         <v>2103</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -16691,7 +16693,7 @@
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="5" t="s">
         <v>2106</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -16705,7 +16707,7 @@
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="5" t="s">
         <v>2109</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -16719,7 +16721,7 @@
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="5" t="s">
         <v>2112</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -16733,7 +16735,7 @@
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="6" t="s">
+      <c r="A61" s="5" t="s">
         <v>2115</v>
       </c>
       <c r="B61" s="3" t="s">
@@ -16747,7 +16749,7 @@
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>2118</v>
       </c>
       <c r="B62" s="3" t="s">
@@ -16761,7 +16763,7 @@
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>2121</v>
       </c>
       <c r="B63" s="3" t="s">
